--- a/consolidado_limpio.xlsx
+++ b/consolidado_limpio.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,7 +690,11 @@
           <t>Laura Diaz</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -818,7 +822,11 @@
           <t>Andres Gomez</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -913,17 +921,21 @@
           <t>Laura Diaz</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chaqueta impermeable</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -932,14 +944,14 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>92100</v>
+        <v>55400</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -951,12 +963,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Audifonos Bluetooth</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -965,10 +977,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>147100</v>
+        <v>20200</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -984,7 +996,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -998,31 +1010,31 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>38100</v>
+        <v>107600</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>No especificado</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1034,28 +1046,28 @@
         <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>55400</v>
+        <v>148600</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Parlante portatil</t>
+          <t>Teclado mecanico</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1064,31 +1076,31 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>20200</v>
+        <v>40700</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Laura Diaz</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1097,60 +1109,64 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>107600</v>
+        <v>74200</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Laura Diaz</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Audifonos Bluetooth</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>148600</v>
+        <v>175600</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Teclado mecanico</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1159,14 +1175,14 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>40700</v>
+        <v>110300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1178,12 +1194,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1195,16 +1211,16 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>74200</v>
+        <v>156100</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>No especificado</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1232,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Audifonos Bluetooth</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1225,31 +1241,31 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>175600</v>
+        <v>41800</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Laura Diaz</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Parlante portatil</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1258,72 +1274,76 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>110300</v>
+        <v>115500</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Mouse inalambrico</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>156100</v>
+        <v>59500</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>Sofia Mena</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tarjeta</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Chaqueta impermeable</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>41800</v>
+        <v>150600</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1332,14 +1352,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>No especificado</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1353,47 +1373,47 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>115500</v>
+        <v>165700</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mouse inalambrico</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>59500</v>
+        <v>80300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1405,74 +1425,78 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chaqueta impermeable</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>150600</v>
+        <v>137900</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Sofia Mena</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>165700</v>
+        <v>74700</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>No especificado</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1481,43 +1505,43 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>80300</v>
+        <v>40200</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>No especificado</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Chaqueta impermeable</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>137900</v>
+        <v>90600</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1526,19 +1550,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>05/07/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1547,22 +1571,26 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>74700</v>
+        <v>98500</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>Andres Gomez</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1576,27 +1604,31 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>40200</v>
+        <v>91350</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>Felipe Torres</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chaqueta impermeable</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1608,7 +1640,7 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>90600</v>
+        <v>125200</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1617,14 +1649,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1638,45 +1670,47 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>98500</v>
+        <v>34000</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
-      </c>
-      <c r="E39" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>133400</v>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1688,74 +1722,78 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>125200</v>
+        <v>164400</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Teclado mecanico</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>34000</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
+        <v>91350</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Andres Gomez</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Mouse inalambrico</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1764,31 +1802,31 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E42" t="n">
-        <v>133400</v>
+        <v>107500</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>05/07/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Parlante portatil</t>
+          <t>Mouse inalambrico</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1797,26 +1835,26 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>164400</v>
+        <v>152700</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1832,10 +1870,12 @@
       <c r="D44" t="n">
         <v>1</v>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>65900</v>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1847,74 +1887,78 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mouse inalambrico</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>107500</v>
+        <v>91350</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Laura Diaz</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No especificado</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mouse inalambrico</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>152700</v>
-      </c>
-      <c r="F46" t="inlineStr"/>
+        <v>157700</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Andres Gomez</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>No especificado</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Teclado mecanico</t>
+          <t>Audifonos Bluetooth</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1923,58 +1967,64 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>65900</v>
+        <v>144100</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
-      </c>
-      <c r="E48" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>78100</v>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>Camila Ruiz</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1983,39 +2033,43 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>157700</v>
+        <v>72700</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>Andres Gomez</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tarjeta</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Audifonos Bluetooth</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E50" t="n">
-        <v>144100</v>
+        <v>78000</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2024,19 +2078,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Parlante portatil</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2048,24 +2102,28 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>78100</v>
+        <v>127500</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>Sofia Mena</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Chaqueta impermeable</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2074,47 +2132,47 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E52" t="n">
-        <v>72700</v>
+        <v>86700</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>78000</v>
+        <v>98800</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2126,7 +2184,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2140,31 +2198,31 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>127500</v>
+        <v>40200</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Andres Gomez</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chaqueta impermeable</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2173,43 +2231,43 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>86700</v>
+        <v>18200</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Laura Diaz</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>98800</v>
+        <v>159900</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2218,118 +2276,118 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Parlante portatil</t>
+          <t>Gorra deportiva</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>40200</v>
+        <v>36200</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Andres Gomez</t>
+          <t>Felipe Torres</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E58" t="n">
-        <v>18200</v>
+        <v>174100</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Laura Diaz</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Transferencia</t>
+          <t>Tarjeta</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jean clasico</t>
+          <t>Cargador USB-C</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Electronica</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
-        <v>159900</v>
+        <v>87300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No especificado</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gorra deportiva</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2338,14 +2396,14 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>36200</v>
+        <v>25600</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Felipe Torres</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2357,28 +2415,28 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Medias deportivas</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>174100</v>
+        <v>26700</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
+          <t>Camila Ruiz</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2390,41 +2448,45 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cargador USB-C</t>
+          <t>Camiseta basica</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Electronica</t>
+          <t>Ropa</t>
         </is>
       </c>
       <c r="D62" t="n">
         <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>87300</v>
+        <v>26700</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sofia Mena</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>Andres Gomez</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Camiseta basica</t>
+          <t>Gorra deportiva</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2433,31 +2495,31 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>25600</v>
+        <v>134400</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Camila Ruiz</t>
+          <t>Sofia Mena</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>No especificado</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Medias deportivas</t>
+          <t>Jean clasico</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2466,10 +2528,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E64" t="n">
-        <v>26700</v>
+        <v>46400</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2478,100 +2540,9 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Camiseta basica</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ropa</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>6</v>
-      </c>
-      <c r="E65" t="n">
-        <v>26700</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Andres Gomez</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Transferencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Gorra deportiva</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ropa</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>3</v>
-      </c>
-      <c r="E66" t="n">
-        <v>134400</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Sofia Mena</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Jean clasico</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ropa</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>7</v>
-      </c>
-      <c r="E67" t="n">
-        <v>46400</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Camila Ruiz</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>No especificado</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidado_limpio.xlsx
+++ b/consolidado_limpio.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,37 +417,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>producto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>cantidad</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>precio_unitario</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>vendedor</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>metodo_pago</t>
         </is>
